--- a/docs/alliance-templates/alliance-enterprises.xlsx
+++ b/docs/alliance-templates/alliance-enterprises.xlsx
@@ -7,28 +7,19 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="合作企业" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作企业'!$A$2:$J$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>填写说明：
-* 必填列。
-企业类型：platform（平台企业） / school-based（校办企业），默认为 platform
-所属行业 / 所在地区：文本，选填
-合作状态：negotiating（洽谈中） / active（合作中） / paused（暂停） / terminated（终止），默认为 active
-合作评级：strategic（战略） / deep（深度） / general（一般），选填
-联系人 / 联系电话 / 联系邮箱 / 企业地址：选填</t>
-  </si>
-  <si>
-    <t>企业名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>企业名称</t>
   </si>
   <si>
     <t>企业类型</t>
@@ -56,13 +47,127 @@
   </si>
   <si>
     <t>企业地址</t>
+  </si>
+  <si>
+    <t>华为技术有限公司</t>
+  </si>
+  <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t>信息技术</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>strategic</t>
+  </si>
+  <si>
+    <t>李明</t>
+  </si>
+  <si>
+    <t>13800138001</t>
+  </si>
+  <si>
+    <t>lm@huawei.com</t>
+  </si>
+  <si>
+    <t>深圳市龙岗区坂田街道</t>
+  </si>
+  <si>
+    <t>阿里巴巴集团</t>
+  </si>
+  <si>
+    <t>互联网/电商</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>王芳</t>
+  </si>
+  <si>
+    <t>13800138002</t>
+  </si>
+  <si>
+    <t>wf@alibaba.com</t>
+  </si>
+  <si>
+    <t>杭州市余杭区文一西路</t>
+  </si>
+  <si>
+    <t>比亚迪股份有限公司</t>
+  </si>
+  <si>
+    <t>新能源汽车</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>张伟</t>
+  </si>
+  <si>
+    <t>13800138003</t>
+  </si>
+  <si>
+    <t>zw@byd.com</t>
+  </si>
+  <si>
+    <t>深圳市坪山区比亚迪路</t>
+  </si>
+  <si>
+    <t>腾讯科技有限公司</t>
+  </si>
+  <si>
+    <t>互联网</t>
+  </si>
+  <si>
+    <t>陈静</t>
+  </si>
+  <si>
+    <t>13800138004</t>
+  </si>
+  <si>
+    <t>cj@tencent.com</t>
+  </si>
+  <si>
+    <t>深圳市南山区科技园</t>
+  </si>
+  <si>
+    <t>中兴通讯股份有限公司</t>
+  </si>
+  <si>
+    <t>通信设备</t>
+  </si>
+  <si>
+    <t>negotiating</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>刘洋</t>
+  </si>
+  <si>
+    <t>13800138005</t>
+  </si>
+  <si>
+    <t>ly@zte.com</t>
+  </si>
+  <si>
+    <t>深圳市南山区高新技术产业园</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,14 +177,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,7 +190,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,34 +202,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -397,70 +480,215 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="4" min="3" width="20"/>
-    <col customWidth="true" max="6" min="5" width="22"/>
-    <col customWidth="true" max="8" min="7" width="18"/>
-    <col customWidth="true" max="9" min="9" width="24"/>
-    <col customWidth="true" max="10" min="10" width="36"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="14"/>
+    <col customWidth="true" max="3" min="3" width="18"/>
+    <col customWidth="true" max="6" min="4" width="14"/>
+    <col customWidth="true" max="7" min="7" width="12"/>
+    <col customWidth="true" max="8" min="8" width="16"/>
+    <col customWidth="true" max="9" min="9" width="22"/>
+    <col customWidth="true" max="10" min="10" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" ht="128" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$J$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$J$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-enterprises.xlsx
+++ b/docs/alliance-templates/alliance-enterprises.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作企业" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,15 +521,15 @@
 联系人 / 联系电话 / 联系邮箱 / 企业地址：选填</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -545,7 +591,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>平台企业</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -560,12 +606,12 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>合作中</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>strategic</t>
+          <t>战略合作</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -597,7 +643,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>平台企业</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -612,12 +658,12 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>合作中</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>strategic</t>
+          <t>战略合作</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -649,7 +695,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>平台企业</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -664,12 +710,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>合作中</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>深度合作</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -701,7 +747,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>平台企业</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -716,12 +762,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>合作中</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>深度合作</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -753,7 +799,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>平台企业</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -768,12 +814,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>negotiating</t>
+          <t>洽谈中</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>一般合作</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
